--- a/tablas/relevamiento.xlsx
+++ b/tablas/relevamiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\florencia\nogal_sanidad\tablas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3F67A8-0E50-425F-85FD-E3169005E22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B223868C-1BC6-4E81-8E7A-0BAD1F888460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tablas/relevamiento.xlsx
+++ b/tablas/relevamiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\florencia\nogal_sanidad\tablas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B223868C-1BC6-4E81-8E7A-0BAD1F888460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661906CC-FDA6-4B9A-880B-93990F9C034F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="45">
   <si>
     <t>finca</t>
   </si>
@@ -188,6 +188,9 @@
   </si>
   <si>
     <t>autumn</t>
+  </si>
+  <si>
+    <t>winter</t>
   </si>
 </sst>
 </file>
@@ -3361,7 +3364,7 @@
         <v>-69.084999999999994</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G53" s="9">
         <v>45446</v>
@@ -3414,7 +3417,7 @@
         <v>-69.174000000000007</v>
       </c>
       <c r="F54" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G54" s="9">
         <v>45510</v>
@@ -3467,7 +3470,7 @@
         <v>-69.174000000000007</v>
       </c>
       <c r="F55" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G55" s="9">
         <v>45510</v>
@@ -3520,7 +3523,7 @@
         <v>-69.174000000000007</v>
       </c>
       <c r="F56" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G56" s="9">
         <v>45510</v>
@@ -3573,7 +3576,7 @@
         <v>-69.174000000000007</v>
       </c>
       <c r="F57" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G57" s="9">
         <v>45510</v>
@@ -3626,7 +3629,7 @@
         <v>-69.052000000000007</v>
       </c>
       <c r="F58" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G58" s="9">
         <v>45511</v>
@@ -3679,7 +3682,7 @@
         <v>-69.052000000000007</v>
       </c>
       <c r="F59" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G59" s="9">
         <v>45511</v>
@@ -3732,7 +3735,7 @@
         <v>-69.052000000000007</v>
       </c>
       <c r="F60" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G60" s="9">
         <v>45511</v>
@@ -3785,7 +3788,7 @@
         <v>-69.052000000000007</v>
       </c>
       <c r="F61" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G61" s="9">
         <v>45511</v>
@@ -3838,7 +3841,7 @@
         <v>-68.463999999999999</v>
       </c>
       <c r="F62" s="18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G62" s="9">
         <v>45551</v>
@@ -3891,7 +3894,7 @@
         <v>-68.463999999999999</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G63" s="9">
         <v>45551</v>
@@ -3944,7 +3947,7 @@
         <v>-68.463999999999999</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G64" s="9">
         <v>45551</v>
@@ -3997,7 +4000,7 @@
         <v>-68.463999999999999</v>
       </c>
       <c r="F65" s="18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G65" s="9">
         <v>45551</v>
@@ -4262,7 +4265,7 @@
         <v>-69.241</v>
       </c>
       <c r="F70" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G70" s="9">
         <v>45726</v>
@@ -4315,7 +4318,7 @@
         <v>-69.241</v>
       </c>
       <c r="F71" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G71" s="9">
         <v>45726</v>
@@ -4368,7 +4371,7 @@
         <v>-69.241</v>
       </c>
       <c r="F72" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G72" s="9">
         <v>45726</v>
@@ -4421,7 +4424,7 @@
         <v>-69.241</v>
       </c>
       <c r="F73" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G73" s="9">
         <v>45726</v>

--- a/tablas/relevamiento.xlsx
+++ b/tablas/relevamiento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\florencia\nogal_sanidad\tablas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661906CC-FDA6-4B9A-880B-93990F9C034F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27573EC5-6C33-4E9A-BE86-B926132D6AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
